--- a/ExcelRAddIn/Tests/Call Python from R.xlsx
+++ b/ExcelRAddIn/Tests/Call Python from R.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Projects\C#\Office\Office365 AddIns\ExcelRAddIn\Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FC02C4-356D-41FE-90CC-3EB2A2688153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA37DC0-7973-4F64-8AA2-95C211AC67D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{C6D9042F-F36C-4DD7-A399-099D864922FA}"/>
   </bookViews>
@@ -78,9 +78,6 @@
     <t>py_last_error()</t>
   </si>
   <si>
-    <t>use_python("C:/Users/adam_/AppData/Local/Programs/Python/Python312")</t>
-  </si>
-  <si>
     <t>library(reticulate)</t>
   </si>
   <si>
@@ -103,6 +100,9 @@
   </si>
   <si>
     <t>source_python("D:/Development/Projects/C#/Office/Office365 AddIns/ExcelRAddIn/Python Scripts/equity_financials_alt.py")</t>
+  </si>
+  <si>
+    <t>use_python("C:/Users/adam_/AppData/Local/Programs/Python/Python314")</t>
   </si>
 </sst>
 </file>
@@ -559,7 +559,7 @@
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="str" cm="1">
         <f t="array" ref="D4">_xll.RScript.Evaluate(B4,TRUE)</f>
@@ -568,11 +568,11 @@
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D6" t="str" cm="1">
         <f t="array" ref="D6">_xll.RScript.Evaluate(B6)</f>
-        <v>C:/Users/adam_/AppData/Local/Programs/Python/Python312/python.exe</v>
+        <v>C:/Users/adam_/AppData/Local/Programs/Python/Python314/python.exe</v>
       </c>
     </row>
   </sheetData>
@@ -609,7 +609,7 @@
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" t="str" cm="1">
         <f t="array" ref="D5">_xll.RScript.Evaluate(B5)</f>
@@ -622,170 +622,58 @@
         <v>tickers</v>
       </c>
       <c r="D7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" t="str" cm="1">
-        <f t="array" ref="D14:J19">_xll.RScript.Evaluate(B14)</f>
-        <v>Index</v>
-      </c>
-      <c r="E14" t="str">
-        <v>ticker</v>
-      </c>
-      <c r="F14" t="str">
-        <v>trailingPE</v>
-      </c>
-      <c r="G14" t="str">
-        <v>forwardPE</v>
-      </c>
-      <c r="H14" t="str">
-        <v>earningsGrowth</v>
-      </c>
-      <c r="I14" t="str">
-        <v>pegRatio</v>
-      </c>
-      <c r="J14" t="str">
-        <v>marketCap</v>
+        <f t="array" ref="D14:D16">_xll.RScript.Evaluate(B14)</f>
+        <v>convert</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="D15" t="str">
-        <v>1</v>
-      </c>
-      <c r="E15" t="str">
-        <v>SAN.MC</v>
-      </c>
-      <c r="F15">
-        <v>6.0236486999999999</v>
-      </c>
-      <c r="G15">
-        <v>5.7549542999999996</v>
-      </c>
-      <c r="H15">
-        <v>0.17699999999999999</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4">
-        <v>68112826368</v>
-      </c>
+        <v>pyobj</v>
+      </c>
+      <c r="J15" s="4"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="D16" t="str">
-        <v>2</v>
-      </c>
-      <c r="E16" t="str">
-        <v>BBVA.MC</v>
-      </c>
-      <c r="F16">
-        <v>5.5862499999999997</v>
-      </c>
-      <c r="G16">
-        <v>5.9622039999999998</v>
-      </c>
-      <c r="H16">
-        <v>0.29299999999999998</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4">
-        <v>51413962752</v>
-      </c>
+        <v>simple</v>
+      </c>
+      <c r="J16" s="4"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="D17" t="str">
-        <v>3</v>
-      </c>
-      <c r="E17" t="str">
-        <v>REP.MC</v>
-      </c>
-      <c r="F17">
-        <v>6.4887642999999997</v>
-      </c>
-      <c r="G17">
-        <v>4.8441890000000001</v>
-      </c>
-      <c r="H17">
-        <v>1.319</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4">
-        <v>13335168000</v>
-      </c>
+      <c r="J17" s="4"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="D18" t="str">
-        <v>4</v>
-      </c>
-      <c r="E18" t="str">
-        <v>MAP.MC</v>
-      </c>
-      <c r="F18">
-        <v>9.0714279999999992</v>
-      </c>
-      <c r="G18">
-        <v>8.0484170000000006</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18" s="4">
-        <v>7787588608</v>
-      </c>
+      <c r="J18" s="4"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="D19" t="str">
-        <v>5</v>
-      </c>
-      <c r="E19" t="str">
-        <v>AENA.MC</v>
-      </c>
-      <c r="F19">
-        <v>15.200616999999999</v>
-      </c>
-      <c r="G19">
-        <v>14.432954000000001</v>
-      </c>
-      <c r="H19">
-        <v>0.21</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4">
-        <v>29550000128</v>
-      </c>
+      <c r="J19" s="4"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
